--- a/sim/resources/sample/Item.xlsx
+++ b/sim/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="175">
   <si>
     <t>道具ID</t>
   </si>
@@ -751,6 +751,9 @@
   </si>
   <si>
     <t>游客升级经验</t>
+  </si>
+  <si>
+    <t>服务能力</t>
   </si>
 </sst>
 </file>
@@ -1986,7 +1989,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -4508,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="s">
         <v>158</v>
@@ -4546,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="s">
         <v>158</v>
@@ -4584,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="s">
         <v>158</v>
@@ -4622,7 +4625,7 @@
         <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="s">
         <v>158</v>
@@ -4660,7 +4663,7 @@
         <v>1</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="s">
         <v>158</v>
@@ -4698,7 +4701,7 @@
         <v>5</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="s">
         <v>158</v>
@@ -4774,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="s">
         <v>158</v>
@@ -4812,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="s">
         <v>158</v>
@@ -4850,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="s">
         <v>158</v>
@@ -4888,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="s">
         <v>158</v>
@@ -4903,6 +4906,44 @@
         <v>173</v>
       </c>
       <c r="O70">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71">
+        <v>1024012</v>
+      </c>
+      <c r="C71">
+        <v>1024012</v>
+      </c>
+      <c r="D71" t="s">
+        <v>174</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="F71" t="s">
+        <v>43</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71" t="s">
+        <v>158</v>
+      </c>
+      <c r="J71">
+        <v>2024012</v>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>174</v>
+      </c>
+      <c r="O71">
         <v>-1</v>
       </c>
     </row>

--- a/sim/resources/sample/Item.xlsx
+++ b/sim/resources/sample/Item.xlsx
@@ -85,7 +85,8 @@
 3：蓝
 4：紫
 5：橙
-6：红</t>
+6：红
+7：金</t>
         </r>
       </text>
     </comment>
@@ -224,12 +225,80 @@
         </r>
       </text>
     </comment>
+    <comment ref="A162" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1026代表雇员类别-导玩员（游戏区）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A172" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1027代表雇员类别-服务员员（休息区）
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A182" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1028代表雇员类别-管理员（管理区）
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="235">
   <si>
     <t>道具ID</t>
   </si>
@@ -754,6 +823,186 @@
   </si>
   <si>
     <t>服务能力</t>
+  </si>
+  <si>
+    <t>街头潮人</t>
+  </si>
+  <si>
+    <t>复古绅士</t>
+  </si>
+  <si>
+    <t>酷盖少年</t>
+  </si>
+  <si>
+    <t>潮流先锋</t>
+  </si>
+  <si>
+    <t>时尚教主</t>
+  </si>
+  <si>
+    <t>街拍达人</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>甜心辣妹</t>
+  </si>
+  <si>
+    <t>活力少女</t>
+  </si>
+  <si>
+    <t>优雅女神</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
+  </si>
+  <si>
+    <t>单车骑士</t>
+  </si>
+  <si>
+    <t>登山行者</t>
+  </si>
+  <si>
+    <t>文艺青年</t>
+  </si>
+  <si>
+    <t>书香少女</t>
+  </si>
+  <si>
+    <t>民谣歌手</t>
+  </si>
+  <si>
+    <t>马拉松客</t>
+  </si>
+  <si>
+    <t>极限玩家</t>
+  </si>
+  <si>
+    <t>科技极客</t>
+  </si>
+  <si>
+    <t>独立画家</t>
+  </si>
+  <si>
+    <t>浪漫诗人</t>
+  </si>
+  <si>
+    <t>古典乐迷</t>
+  </si>
+  <si>
+    <t>创业新贵</t>
+  </si>
+  <si>
+    <t>摸金校尉</t>
+  </si>
+  <si>
+    <t>氪金大佬</t>
+  </si>
+  <si>
+    <t>穿搭博主</t>
+  </si>
+  <si>
+    <t>美妆新秀</t>
+  </si>
+  <si>
+    <t>高定女王</t>
+  </si>
+  <si>
+    <t>威廉</t>
+  </si>
+  <si>
+    <t>艾拉</t>
+  </si>
+  <si>
+    <t>亨利</t>
+  </si>
+  <si>
+    <t>艾玛</t>
+  </si>
+  <si>
+    <t>乔治</t>
+  </si>
+  <si>
+    <t>艾娃</t>
+  </si>
+  <si>
+    <t>亚瑟</t>
+  </si>
+  <si>
+    <t>安娜</t>
+  </si>
+  <si>
+    <t>马修</t>
+  </si>
+  <si>
+    <t>哈珀</t>
+  </si>
+  <si>
+    <t>拉斐尔</t>
+  </si>
+  <si>
+    <t>伊芙琳</t>
+  </si>
+  <si>
+    <t>埃米尔</t>
+  </si>
+  <si>
+    <t>夏洛特</t>
+  </si>
+  <si>
+    <t>雷蒙德</t>
+  </si>
+  <si>
+    <t>斯嘉丽</t>
+  </si>
+  <si>
+    <t>丹尼尔</t>
+  </si>
+  <si>
+    <t>莉莉安</t>
+  </si>
+  <si>
+    <t>卢卡斯</t>
+  </si>
+  <si>
+    <t>克拉拉</t>
+  </si>
+  <si>
+    <t>尼古拉斯</t>
+  </si>
+  <si>
+    <t>奥利维亚</t>
+  </si>
+  <si>
+    <t>亚历山大</t>
+  </si>
+  <si>
+    <t>玛格丽特</t>
+  </si>
+  <si>
+    <t>奥古斯特</t>
+  </si>
+  <si>
+    <t>维奥莱特</t>
+  </si>
+  <si>
+    <t>费利克斯</t>
+  </si>
+  <si>
+    <t>维多利亚</t>
+  </si>
+  <si>
+    <t>阿尔弗雷德</t>
+  </si>
+  <si>
+    <t>伊丽莎白</t>
   </si>
 </sst>
 </file>
@@ -1989,7 +2238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R191"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -4947,6 +5196,4686 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="72" spans="1:15">
+      <c r="A72">
+        <v>1025101</v>
+      </c>
+      <c r="C72">
+        <v>1025101</v>
+      </c>
+      <c r="D72" t="s">
+        <v>175</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72" t="s">
+        <v>43</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>158</v>
+      </c>
+      <c r="J72">
+        <v>2025101</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="s">
+        <v>175</v>
+      </c>
+      <c r="O72">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73">
+        <v>1025102</v>
+      </c>
+      <c r="C73">
+        <v>1025102</v>
+      </c>
+      <c r="D73" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73" t="s">
+        <v>43</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>158</v>
+      </c>
+      <c r="J73">
+        <v>2025102</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>176</v>
+      </c>
+      <c r="O73">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74">
+        <v>1025103</v>
+      </c>
+      <c r="C74">
+        <v>1025103</v>
+      </c>
+      <c r="D74" t="s">
+        <v>177</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74" t="s">
+        <v>43</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>158</v>
+      </c>
+      <c r="J74">
+        <v>2025103</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>177</v>
+      </c>
+      <c r="O74">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75">
+        <v>1025104</v>
+      </c>
+      <c r="C75">
+        <v>1025104</v>
+      </c>
+      <c r="D75" t="s">
+        <v>178</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75" t="s">
+        <v>43</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>158</v>
+      </c>
+      <c r="J75">
+        <v>2025104</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
+        <v>178</v>
+      </c>
+      <c r="O75">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76">
+        <v>1025105</v>
+      </c>
+      <c r="C76">
+        <v>1025105</v>
+      </c>
+      <c r="D76" t="s">
+        <v>179</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76" t="s">
+        <v>158</v>
+      </c>
+      <c r="J76">
+        <v>2025105</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>179</v>
+      </c>
+      <c r="O76">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77">
+        <v>1025106</v>
+      </c>
+      <c r="C77">
+        <v>1025106</v>
+      </c>
+      <c r="D77" t="s">
+        <v>180</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="F77" t="s">
+        <v>43</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77" t="s">
+        <v>158</v>
+      </c>
+      <c r="J77">
+        <v>2025106</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>180</v>
+      </c>
+      <c r="O77">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78">
+        <v>1025201</v>
+      </c>
+      <c r="C78">
+        <v>1025201</v>
+      </c>
+      <c r="D78" t="s">
+        <v>181</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78" t="s">
+        <v>43</v>
+      </c>
+      <c r="G78">
+        <v>2</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>158</v>
+      </c>
+      <c r="J78">
+        <v>2025201</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>181</v>
+      </c>
+      <c r="O78">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79">
+        <v>1025202</v>
+      </c>
+      <c r="C79">
+        <v>1025202</v>
+      </c>
+      <c r="D79" t="s">
+        <v>182</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+      <c r="F79" t="s">
+        <v>43</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>158</v>
+      </c>
+      <c r="J79">
+        <v>2025202</v>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
+        <v>182</v>
+      </c>
+      <c r="O79">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80">
+        <v>1025203</v>
+      </c>
+      <c r="C80">
+        <v>1025203</v>
+      </c>
+      <c r="D80" t="s">
+        <v>183</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="F80" t="s">
+        <v>43</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80" t="s">
+        <v>158</v>
+      </c>
+      <c r="J80">
+        <v>2025203</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>183</v>
+      </c>
+      <c r="O80">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81">
+        <v>1025204</v>
+      </c>
+      <c r="C81">
+        <v>1025204</v>
+      </c>
+      <c r="D81" t="s">
+        <v>184</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="F81" t="s">
+        <v>43</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81" t="s">
+        <v>158</v>
+      </c>
+      <c r="J81">
+        <v>2025204</v>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
+        <v>184</v>
+      </c>
+      <c r="O81">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82">
+        <v>1025205</v>
+      </c>
+      <c r="C82">
+        <v>1025205</v>
+      </c>
+      <c r="D82" t="s">
+        <v>185</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="F82" t="s">
+        <v>43</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82" t="s">
+        <v>158</v>
+      </c>
+      <c r="J82">
+        <v>2025205</v>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
+        <v>185</v>
+      </c>
+      <c r="O82">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83">
+        <v>1025206</v>
+      </c>
+      <c r="C83">
+        <v>1025206</v>
+      </c>
+      <c r="D83" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83" t="s">
+        <v>43</v>
+      </c>
+      <c r="G83">
+        <v>2</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83" t="s">
+        <v>158</v>
+      </c>
+      <c r="J83">
+        <v>2025206</v>
+      </c>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
+        <v>186</v>
+      </c>
+      <c r="O83">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84">
+        <v>1025301</v>
+      </c>
+      <c r="C84">
+        <v>1025301</v>
+      </c>
+      <c r="D84" t="s">
+        <v>187</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="F84" t="s">
+        <v>43</v>
+      </c>
+      <c r="G84">
+        <v>3</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84" t="s">
+        <v>158</v>
+      </c>
+      <c r="J84">
+        <v>2025301</v>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
+        <v>187</v>
+      </c>
+      <c r="O84">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85">
+        <v>1025302</v>
+      </c>
+      <c r="C85">
+        <v>1025302</v>
+      </c>
+      <c r="D85" t="s">
+        <v>188</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="F85" t="s">
+        <v>43</v>
+      </c>
+      <c r="G85">
+        <v>3</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85" t="s">
+        <v>158</v>
+      </c>
+      <c r="J85">
+        <v>2025302</v>
+      </c>
+      <c r="K85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>188</v>
+      </c>
+      <c r="O85">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86">
+        <v>1025303</v>
+      </c>
+      <c r="C86">
+        <v>1025303</v>
+      </c>
+      <c r="D86" t="s">
+        <v>189</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="F86" t="s">
+        <v>43</v>
+      </c>
+      <c r="G86">
+        <v>3</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86" t="s">
+        <v>158</v>
+      </c>
+      <c r="J86">
+        <v>2025303</v>
+      </c>
+      <c r="K86" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
+        <v>189</v>
+      </c>
+      <c r="O86">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87">
+        <v>1025304</v>
+      </c>
+      <c r="C87">
+        <v>1025304</v>
+      </c>
+      <c r="D87" t="s">
+        <v>190</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87" t="s">
+        <v>43</v>
+      </c>
+      <c r="G87">
+        <v>3</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87" t="s">
+        <v>158</v>
+      </c>
+      <c r="J87">
+        <v>2025304</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
+        <v>190</v>
+      </c>
+      <c r="O87">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88">
+        <v>1025305</v>
+      </c>
+      <c r="C88">
+        <v>1025305</v>
+      </c>
+      <c r="D88" t="s">
+        <v>191</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88" t="s">
+        <v>43</v>
+      </c>
+      <c r="G88">
+        <v>3</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88" t="s">
+        <v>158</v>
+      </c>
+      <c r="J88">
+        <v>2025305</v>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
+        <v>191</v>
+      </c>
+      <c r="O88">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89">
+        <v>1025306</v>
+      </c>
+      <c r="C89">
+        <v>1025306</v>
+      </c>
+      <c r="D89" t="s">
+        <v>192</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89" t="s">
+        <v>43</v>
+      </c>
+      <c r="G89">
+        <v>3</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89" t="s">
+        <v>158</v>
+      </c>
+      <c r="J89">
+        <v>2025306</v>
+      </c>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" t="s">
+        <v>192</v>
+      </c>
+      <c r="O89">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90">
+        <v>1025401</v>
+      </c>
+      <c r="C90">
+        <v>1025401</v>
+      </c>
+      <c r="D90" t="s">
+        <v>193</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="F90" t="s">
+        <v>43</v>
+      </c>
+      <c r="G90">
+        <v>4</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90" t="s">
+        <v>158</v>
+      </c>
+      <c r="J90">
+        <v>2025401</v>
+      </c>
+      <c r="K90" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90" t="s">
+        <v>193</v>
+      </c>
+      <c r="O90">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91">
+        <v>1025402</v>
+      </c>
+      <c r="C91">
+        <v>1025402</v>
+      </c>
+      <c r="D91" t="s">
+        <v>194</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="F91" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91">
+        <v>4</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91" t="s">
+        <v>158</v>
+      </c>
+      <c r="J91">
+        <v>2025402</v>
+      </c>
+      <c r="K91" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" t="s">
+        <v>194</v>
+      </c>
+      <c r="O91">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92">
+        <v>1025403</v>
+      </c>
+      <c r="C92">
+        <v>1025403</v>
+      </c>
+      <c r="D92" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="F92" t="s">
+        <v>43</v>
+      </c>
+      <c r="G92">
+        <v>4</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92" t="s">
+        <v>158</v>
+      </c>
+      <c r="J92">
+        <v>2025403</v>
+      </c>
+      <c r="K92" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
+        <v>195</v>
+      </c>
+      <c r="O92">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93">
+        <v>1025404</v>
+      </c>
+      <c r="C93">
+        <v>1025404</v>
+      </c>
+      <c r="D93" t="s">
+        <v>196</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93">
+        <v>4</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93" t="s">
+        <v>158</v>
+      </c>
+      <c r="J93">
+        <v>2025404</v>
+      </c>
+      <c r="K93" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
+        <v>196</v>
+      </c>
+      <c r="O93">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94">
+        <v>1025405</v>
+      </c>
+      <c r="C94">
+        <v>1025405</v>
+      </c>
+      <c r="D94" t="s">
+        <v>197</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+      <c r="F94" t="s">
+        <v>43</v>
+      </c>
+      <c r="G94">
+        <v>4</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94" t="s">
+        <v>158</v>
+      </c>
+      <c r="J94">
+        <v>2025405</v>
+      </c>
+      <c r="K94" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" t="s">
+        <v>197</v>
+      </c>
+      <c r="O94">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95">
+        <v>1025406</v>
+      </c>
+      <c r="C95">
+        <v>1025406</v>
+      </c>
+      <c r="D95" t="s">
+        <v>198</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="F95" t="s">
+        <v>43</v>
+      </c>
+      <c r="G95">
+        <v>4</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95" t="s">
+        <v>158</v>
+      </c>
+      <c r="J95">
+        <v>2025406</v>
+      </c>
+      <c r="K95" t="b">
+        <v>0</v>
+      </c>
+      <c r="L95" t="s">
+        <v>198</v>
+      </c>
+      <c r="O95">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96">
+        <v>1025501</v>
+      </c>
+      <c r="C96">
+        <v>1025501</v>
+      </c>
+      <c r="D96" t="s">
+        <v>199</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="F96" t="s">
+        <v>43</v>
+      </c>
+      <c r="G96">
+        <v>7</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96" t="s">
+        <v>158</v>
+      </c>
+      <c r="J96">
+        <v>2025501</v>
+      </c>
+      <c r="K96" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" t="s">
+        <v>199</v>
+      </c>
+      <c r="O96">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97">
+        <v>1025502</v>
+      </c>
+      <c r="C97">
+        <v>1025502</v>
+      </c>
+      <c r="D97" t="s">
+        <v>200</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="F97" t="s">
+        <v>43</v>
+      </c>
+      <c r="G97">
+        <v>7</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97" t="s">
+        <v>158</v>
+      </c>
+      <c r="J97">
+        <v>2025502</v>
+      </c>
+      <c r="K97" t="b">
+        <v>0</v>
+      </c>
+      <c r="L97" t="s">
+        <v>200</v>
+      </c>
+      <c r="O97">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98">
+        <v>1025503</v>
+      </c>
+      <c r="C98">
+        <v>1025503</v>
+      </c>
+      <c r="D98" t="s">
+        <v>201</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="F98" t="s">
+        <v>43</v>
+      </c>
+      <c r="G98">
+        <v>7</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98" t="s">
+        <v>158</v>
+      </c>
+      <c r="J98">
+        <v>2025503</v>
+      </c>
+      <c r="K98" t="b">
+        <v>0</v>
+      </c>
+      <c r="L98" t="s">
+        <v>201</v>
+      </c>
+      <c r="O98">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99">
+        <v>1025504</v>
+      </c>
+      <c r="C99">
+        <v>1025504</v>
+      </c>
+      <c r="D99" t="s">
+        <v>202</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99" t="s">
+        <v>43</v>
+      </c>
+      <c r="G99">
+        <v>7</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99" t="s">
+        <v>158</v>
+      </c>
+      <c r="J99">
+        <v>2025504</v>
+      </c>
+      <c r="K99" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99" t="s">
+        <v>202</v>
+      </c>
+      <c r="O99">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100">
+        <v>1025505</v>
+      </c>
+      <c r="C100">
+        <v>1025505</v>
+      </c>
+      <c r="D100" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="F100" t="s">
+        <v>43</v>
+      </c>
+      <c r="G100">
+        <v>7</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100" t="s">
+        <v>158</v>
+      </c>
+      <c r="J100">
+        <v>2025505</v>
+      </c>
+      <c r="K100" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100" t="s">
+        <v>203</v>
+      </c>
+      <c r="O100">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101">
+        <v>1025506</v>
+      </c>
+      <c r="C101">
+        <v>1025506</v>
+      </c>
+      <c r="D101" t="s">
+        <v>204</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+      <c r="F101" t="s">
+        <v>43</v>
+      </c>
+      <c r="G101">
+        <v>7</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101" t="s">
+        <v>158</v>
+      </c>
+      <c r="J101">
+        <v>2025506</v>
+      </c>
+      <c r="K101" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" t="s">
+        <v>204</v>
+      </c>
+      <c r="O101">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102">
+        <v>1125101</v>
+      </c>
+      <c r="C102">
+        <v>1125101</v>
+      </c>
+      <c r="D102" t="str">
+        <f>D72&amp;"碎片"</f>
+        <v>街头潮人碎片</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="F102" t="s">
+        <v>43</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102" t="s">
+        <v>158</v>
+      </c>
+      <c r="J102">
+        <v>2125101</v>
+      </c>
+      <c r="K102" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" t="str">
+        <f>D72&amp;"游客的升星道具"</f>
+        <v>街头潮人游客的升星道具</v>
+      </c>
+      <c r="O102">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103">
+        <v>1125102</v>
+      </c>
+      <c r="C103">
+        <v>1125102</v>
+      </c>
+      <c r="D103" t="str">
+        <f t="shared" ref="D103:D131" si="0">D73&amp;"碎片"</f>
+        <v>复古绅士碎片</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103" t="s">
+        <v>43</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103" t="s">
+        <v>158</v>
+      </c>
+      <c r="J103">
+        <v>2125102</v>
+      </c>
+      <c r="K103" t="b">
+        <v>0</v>
+      </c>
+      <c r="L103" t="str">
+        <f t="shared" ref="L103:L131" si="1">D73&amp;"游客的升星道具"</f>
+        <v>复古绅士游客的升星道具</v>
+      </c>
+      <c r="O103">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104">
+        <v>1125103</v>
+      </c>
+      <c r="C104">
+        <v>1125103</v>
+      </c>
+      <c r="D104" t="str">
+        <f t="shared" si="0"/>
+        <v>酷盖少年碎片</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="F104" t="s">
+        <v>43</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104" t="s">
+        <v>158</v>
+      </c>
+      <c r="J104">
+        <v>2125103</v>
+      </c>
+      <c r="K104" t="b">
+        <v>0</v>
+      </c>
+      <c r="L104" t="str">
+        <f t="shared" si="1"/>
+        <v>酷盖少年游客的升星道具</v>
+      </c>
+      <c r="O104">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105">
+        <v>1125104</v>
+      </c>
+      <c r="C105">
+        <v>1125104</v>
+      </c>
+      <c r="D105" t="str">
+        <f t="shared" si="0"/>
+        <v>潮流先锋碎片</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="F105" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105" t="s">
+        <v>158</v>
+      </c>
+      <c r="J105">
+        <v>2125104</v>
+      </c>
+      <c r="K105" t="b">
+        <v>0</v>
+      </c>
+      <c r="L105" t="str">
+        <f t="shared" si="1"/>
+        <v>潮流先锋游客的升星道具</v>
+      </c>
+      <c r="O105">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106">
+        <v>1125105</v>
+      </c>
+      <c r="C106">
+        <v>1125105</v>
+      </c>
+      <c r="D106" t="str">
+        <f t="shared" si="0"/>
+        <v>时尚教主碎片</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106" t="s">
+        <v>43</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106" t="s">
+        <v>158</v>
+      </c>
+      <c r="J106">
+        <v>2125105</v>
+      </c>
+      <c r="K106" t="b">
+        <v>0</v>
+      </c>
+      <c r="L106" t="str">
+        <f t="shared" si="1"/>
+        <v>时尚教主游客的升星道具</v>
+      </c>
+      <c r="O106">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107">
+        <v>1125106</v>
+      </c>
+      <c r="C107">
+        <v>1125106</v>
+      </c>
+      <c r="D107" t="str">
+        <f t="shared" si="0"/>
+        <v>街拍达人碎片</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="F107" t="s">
+        <v>43</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107" t="s">
+        <v>158</v>
+      </c>
+      <c r="J107">
+        <v>2125106</v>
+      </c>
+      <c r="K107" t="b">
+        <v>0</v>
+      </c>
+      <c r="L107" t="str">
+        <f t="shared" si="1"/>
+        <v>街拍达人游客的升星道具</v>
+      </c>
+      <c r="O107">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108">
+        <v>1125201</v>
+      </c>
+      <c r="C108">
+        <v>1125201</v>
+      </c>
+      <c r="D108" t="str">
+        <f t="shared" si="0"/>
+        <v>运动健将碎片</v>
+      </c>
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="F108" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108">
+        <v>2</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108" t="s">
+        <v>158</v>
+      </c>
+      <c r="J108">
+        <v>2125201</v>
+      </c>
+      <c r="K108" t="b">
+        <v>0</v>
+      </c>
+      <c r="L108" t="str">
+        <f t="shared" si="1"/>
+        <v>运动健将游客的升星道具</v>
+      </c>
+      <c r="O108">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109">
+        <v>1125202</v>
+      </c>
+      <c r="C109">
+        <v>1125202</v>
+      </c>
+      <c r="D109" t="str">
+        <f t="shared" si="0"/>
+        <v>跑酷少年碎片</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="F109" t="s">
+        <v>43</v>
+      </c>
+      <c r="G109">
+        <v>2</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109" t="s">
+        <v>158</v>
+      </c>
+      <c r="J109">
+        <v>2125202</v>
+      </c>
+      <c r="K109" t="b">
+        <v>0</v>
+      </c>
+      <c r="L109" t="str">
+        <f t="shared" si="1"/>
+        <v>跑酷少年游客的升星道具</v>
+      </c>
+      <c r="O109">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110">
+        <v>1125203</v>
+      </c>
+      <c r="C110">
+        <v>1125203</v>
+      </c>
+      <c r="D110" t="str">
+        <f t="shared" si="0"/>
+        <v>滑板高手碎片</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="F110" t="s">
+        <v>43</v>
+      </c>
+      <c r="G110">
+        <v>2</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110" t="s">
+        <v>158</v>
+      </c>
+      <c r="J110">
+        <v>2125203</v>
+      </c>
+      <c r="K110" t="b">
+        <v>0</v>
+      </c>
+      <c r="L110" t="str">
+        <f t="shared" si="1"/>
+        <v>滑板高手游客的升星道具</v>
+      </c>
+      <c r="O110">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111">
+        <v>1125204</v>
+      </c>
+      <c r="C111">
+        <v>1125204</v>
+      </c>
+      <c r="D111" t="str">
+        <f t="shared" si="0"/>
+        <v>甜心辣妹碎片</v>
+      </c>
+      <c r="E111">
+        <v>2</v>
+      </c>
+      <c r="F111" t="s">
+        <v>43</v>
+      </c>
+      <c r="G111">
+        <v>2</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111" t="s">
+        <v>158</v>
+      </c>
+      <c r="J111">
+        <v>2125204</v>
+      </c>
+      <c r="K111" t="b">
+        <v>0</v>
+      </c>
+      <c r="L111" t="str">
+        <f t="shared" si="1"/>
+        <v>甜心辣妹游客的升星道具</v>
+      </c>
+      <c r="O111">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112">
+        <v>1125205</v>
+      </c>
+      <c r="C112">
+        <v>1125205</v>
+      </c>
+      <c r="D112" t="str">
+        <f t="shared" si="0"/>
+        <v>活力少女碎片</v>
+      </c>
+      <c r="E112">
+        <v>2</v>
+      </c>
+      <c r="F112" t="s">
+        <v>43</v>
+      </c>
+      <c r="G112">
+        <v>2</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112" t="s">
+        <v>158</v>
+      </c>
+      <c r="J112">
+        <v>2125205</v>
+      </c>
+      <c r="K112" t="b">
+        <v>0</v>
+      </c>
+      <c r="L112" t="str">
+        <f t="shared" si="1"/>
+        <v>活力少女游客的升星道具</v>
+      </c>
+      <c r="O112">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113">
+        <v>1125206</v>
+      </c>
+      <c r="C113">
+        <v>1125206</v>
+      </c>
+      <c r="D113" t="str">
+        <f t="shared" si="0"/>
+        <v>优雅女神碎片</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113" t="s">
+        <v>43</v>
+      </c>
+      <c r="G113">
+        <v>2</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="I113" t="s">
+        <v>158</v>
+      </c>
+      <c r="J113">
+        <v>2125206</v>
+      </c>
+      <c r="K113" t="b">
+        <v>0</v>
+      </c>
+      <c r="L113" t="str">
+        <f t="shared" si="1"/>
+        <v>优雅女神游客的升星道具</v>
+      </c>
+      <c r="O113">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114">
+        <v>1125301</v>
+      </c>
+      <c r="C114">
+        <v>1125301</v>
+      </c>
+      <c r="D114" t="str">
+        <f t="shared" si="0"/>
+        <v>健身狂魔碎片</v>
+      </c>
+      <c r="E114">
+        <v>2</v>
+      </c>
+      <c r="F114" t="s">
+        <v>43</v>
+      </c>
+      <c r="G114">
+        <v>3</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114" t="s">
+        <v>158</v>
+      </c>
+      <c r="J114">
+        <v>2125301</v>
+      </c>
+      <c r="K114" t="b">
+        <v>0</v>
+      </c>
+      <c r="L114" t="str">
+        <f t="shared" si="1"/>
+        <v>健身狂魔游客的升星道具</v>
+      </c>
+      <c r="O114">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115">
+        <v>1125302</v>
+      </c>
+      <c r="C115">
+        <v>1125302</v>
+      </c>
+      <c r="D115" t="str">
+        <f t="shared" si="0"/>
+        <v>单车骑士碎片</v>
+      </c>
+      <c r="E115">
+        <v>2</v>
+      </c>
+      <c r="F115" t="s">
+        <v>43</v>
+      </c>
+      <c r="G115">
+        <v>3</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115" t="s">
+        <v>158</v>
+      </c>
+      <c r="J115">
+        <v>2125302</v>
+      </c>
+      <c r="K115" t="b">
+        <v>0</v>
+      </c>
+      <c r="L115" t="str">
+        <f t="shared" si="1"/>
+        <v>单车骑士游客的升星道具</v>
+      </c>
+      <c r="O115">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116">
+        <v>1125303</v>
+      </c>
+      <c r="C116">
+        <v>1125303</v>
+      </c>
+      <c r="D116" t="str">
+        <f t="shared" si="0"/>
+        <v>登山行者碎片</v>
+      </c>
+      <c r="E116">
+        <v>2</v>
+      </c>
+      <c r="F116" t="s">
+        <v>43</v>
+      </c>
+      <c r="G116">
+        <v>3</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116" t="s">
+        <v>158</v>
+      </c>
+      <c r="J116">
+        <v>2125303</v>
+      </c>
+      <c r="K116" t="b">
+        <v>0</v>
+      </c>
+      <c r="L116" t="str">
+        <f t="shared" si="1"/>
+        <v>登山行者游客的升星道具</v>
+      </c>
+      <c r="O116">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117">
+        <v>1125304</v>
+      </c>
+      <c r="C117">
+        <v>1125304</v>
+      </c>
+      <c r="D117" t="str">
+        <f t="shared" si="0"/>
+        <v>文艺青年碎片</v>
+      </c>
+      <c r="E117">
+        <v>2</v>
+      </c>
+      <c r="F117" t="s">
+        <v>43</v>
+      </c>
+      <c r="G117">
+        <v>3</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117" t="s">
+        <v>158</v>
+      </c>
+      <c r="J117">
+        <v>2125304</v>
+      </c>
+      <c r="K117" t="b">
+        <v>0</v>
+      </c>
+      <c r="L117" t="str">
+        <f t="shared" si="1"/>
+        <v>文艺青年游客的升星道具</v>
+      </c>
+      <c r="O117">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118">
+        <v>1125305</v>
+      </c>
+      <c r="C118">
+        <v>1125305</v>
+      </c>
+      <c r="D118" t="str">
+        <f t="shared" si="0"/>
+        <v>书香少女碎片</v>
+      </c>
+      <c r="E118">
+        <v>2</v>
+      </c>
+      <c r="F118" t="s">
+        <v>43</v>
+      </c>
+      <c r="G118">
+        <v>3</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118" t="s">
+        <v>158</v>
+      </c>
+      <c r="J118">
+        <v>2125305</v>
+      </c>
+      <c r="K118" t="b">
+        <v>0</v>
+      </c>
+      <c r="L118" t="str">
+        <f t="shared" si="1"/>
+        <v>书香少女游客的升星道具</v>
+      </c>
+      <c r="O118">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119">
+        <v>1125306</v>
+      </c>
+      <c r="C119">
+        <v>1125306</v>
+      </c>
+      <c r="D119" t="str">
+        <f t="shared" si="0"/>
+        <v>民谣歌手碎片</v>
+      </c>
+      <c r="E119">
+        <v>2</v>
+      </c>
+      <c r="F119" t="s">
+        <v>43</v>
+      </c>
+      <c r="G119">
+        <v>3</v>
+      </c>
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="I119" t="s">
+        <v>158</v>
+      </c>
+      <c r="J119">
+        <v>2125306</v>
+      </c>
+      <c r="K119" t="b">
+        <v>0</v>
+      </c>
+      <c r="L119" t="str">
+        <f t="shared" si="1"/>
+        <v>民谣歌手游客的升星道具</v>
+      </c>
+      <c r="O119">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120">
+        <v>1125401</v>
+      </c>
+      <c r="C120">
+        <v>1125401</v>
+      </c>
+      <c r="D120" t="str">
+        <f t="shared" si="0"/>
+        <v>马拉松客碎片</v>
+      </c>
+      <c r="E120">
+        <v>2</v>
+      </c>
+      <c r="F120" t="s">
+        <v>43</v>
+      </c>
+      <c r="G120">
+        <v>4</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120" t="s">
+        <v>158</v>
+      </c>
+      <c r="J120">
+        <v>2125401</v>
+      </c>
+      <c r="K120" t="b">
+        <v>0</v>
+      </c>
+      <c r="L120" t="str">
+        <f t="shared" si="1"/>
+        <v>马拉松客游客的升星道具</v>
+      </c>
+      <c r="O120">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121">
+        <v>1125402</v>
+      </c>
+      <c r="C121">
+        <v>1125402</v>
+      </c>
+      <c r="D121" t="str">
+        <f t="shared" si="0"/>
+        <v>极限玩家碎片</v>
+      </c>
+      <c r="E121">
+        <v>2</v>
+      </c>
+      <c r="F121" t="s">
+        <v>43</v>
+      </c>
+      <c r="G121">
+        <v>4</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121" t="s">
+        <v>158</v>
+      </c>
+      <c r="J121">
+        <v>2125402</v>
+      </c>
+      <c r="K121" t="b">
+        <v>0</v>
+      </c>
+      <c r="L121" t="str">
+        <f t="shared" si="1"/>
+        <v>极限玩家游客的升星道具</v>
+      </c>
+      <c r="O121">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
+      <c r="A122">
+        <v>1125403</v>
+      </c>
+      <c r="C122">
+        <v>1125403</v>
+      </c>
+      <c r="D122" t="str">
+        <f t="shared" si="0"/>
+        <v>科技极客碎片</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122" t="s">
+        <v>43</v>
+      </c>
+      <c r="G122">
+        <v>4</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122" t="s">
+        <v>158</v>
+      </c>
+      <c r="J122">
+        <v>2125403</v>
+      </c>
+      <c r="K122" t="b">
+        <v>0</v>
+      </c>
+      <c r="L122" t="str">
+        <f t="shared" si="1"/>
+        <v>科技极客游客的升星道具</v>
+      </c>
+      <c r="O122">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
+      <c r="A123">
+        <v>1125404</v>
+      </c>
+      <c r="C123">
+        <v>1125404</v>
+      </c>
+      <c r="D123" t="str">
+        <f t="shared" si="0"/>
+        <v>独立画家碎片</v>
+      </c>
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123" t="s">
+        <v>43</v>
+      </c>
+      <c r="G123">
+        <v>4</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123" t="s">
+        <v>158</v>
+      </c>
+      <c r="J123">
+        <v>2125404</v>
+      </c>
+      <c r="K123" t="b">
+        <v>0</v>
+      </c>
+      <c r="L123" t="str">
+        <f t="shared" si="1"/>
+        <v>独立画家游客的升星道具</v>
+      </c>
+      <c r="O123">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
+      <c r="A124">
+        <v>1125405</v>
+      </c>
+      <c r="C124">
+        <v>1125405</v>
+      </c>
+      <c r="D124" t="str">
+        <f t="shared" si="0"/>
+        <v>浪漫诗人碎片</v>
+      </c>
+      <c r="E124">
+        <v>2</v>
+      </c>
+      <c r="F124" t="s">
+        <v>43</v>
+      </c>
+      <c r="G124">
+        <v>4</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124" t="s">
+        <v>158</v>
+      </c>
+      <c r="J124">
+        <v>2125405</v>
+      </c>
+      <c r="K124" t="b">
+        <v>0</v>
+      </c>
+      <c r="L124" t="str">
+        <f t="shared" si="1"/>
+        <v>浪漫诗人游客的升星道具</v>
+      </c>
+      <c r="O124">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
+      <c r="A125">
+        <v>1125406</v>
+      </c>
+      <c r="C125">
+        <v>1125406</v>
+      </c>
+      <c r="D125" t="str">
+        <f t="shared" si="0"/>
+        <v>古典乐迷碎片</v>
+      </c>
+      <c r="E125">
+        <v>2</v>
+      </c>
+      <c r="F125" t="s">
+        <v>43</v>
+      </c>
+      <c r="G125">
+        <v>4</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="I125" t="s">
+        <v>158</v>
+      </c>
+      <c r="J125">
+        <v>2125406</v>
+      </c>
+      <c r="K125" t="b">
+        <v>0</v>
+      </c>
+      <c r="L125" t="str">
+        <f t="shared" si="1"/>
+        <v>古典乐迷游客的升星道具</v>
+      </c>
+      <c r="O125">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
+      <c r="A126">
+        <v>1125501</v>
+      </c>
+      <c r="C126">
+        <v>1125501</v>
+      </c>
+      <c r="D126" t="str">
+        <f t="shared" si="0"/>
+        <v>创业新贵碎片</v>
+      </c>
+      <c r="E126">
+        <v>2</v>
+      </c>
+      <c r="F126" t="s">
+        <v>43</v>
+      </c>
+      <c r="G126">
+        <v>7</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126" t="s">
+        <v>158</v>
+      </c>
+      <c r="J126">
+        <v>2125501</v>
+      </c>
+      <c r="K126" t="b">
+        <v>0</v>
+      </c>
+      <c r="L126" t="str">
+        <f t="shared" si="1"/>
+        <v>创业新贵游客的升星道具</v>
+      </c>
+      <c r="O126">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
+      <c r="A127">
+        <v>1125502</v>
+      </c>
+      <c r="C127">
+        <v>1125502</v>
+      </c>
+      <c r="D127" t="str">
+        <f t="shared" si="0"/>
+        <v>摸金校尉碎片</v>
+      </c>
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127" t="s">
+        <v>43</v>
+      </c>
+      <c r="G127">
+        <v>7</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127" t="s">
+        <v>158</v>
+      </c>
+      <c r="J127">
+        <v>2125502</v>
+      </c>
+      <c r="K127" t="b">
+        <v>0</v>
+      </c>
+      <c r="L127" t="str">
+        <f t="shared" si="1"/>
+        <v>摸金校尉游客的升星道具</v>
+      </c>
+      <c r="O127">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
+      <c r="A128">
+        <v>1125503</v>
+      </c>
+      <c r="C128">
+        <v>1125503</v>
+      </c>
+      <c r="D128" t="str">
+        <f t="shared" si="0"/>
+        <v>氪金大佬碎片</v>
+      </c>
+      <c r="E128">
+        <v>2</v>
+      </c>
+      <c r="F128" t="s">
+        <v>43</v>
+      </c>
+      <c r="G128">
+        <v>7</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128" t="s">
+        <v>158</v>
+      </c>
+      <c r="J128">
+        <v>2125503</v>
+      </c>
+      <c r="K128" t="b">
+        <v>0</v>
+      </c>
+      <c r="L128" t="str">
+        <f t="shared" si="1"/>
+        <v>氪金大佬游客的升星道具</v>
+      </c>
+      <c r="O128">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
+      <c r="A129">
+        <v>1125504</v>
+      </c>
+      <c r="C129">
+        <v>1125504</v>
+      </c>
+      <c r="D129" t="str">
+        <f t="shared" si="0"/>
+        <v>穿搭博主碎片</v>
+      </c>
+      <c r="E129">
+        <v>2</v>
+      </c>
+      <c r="F129" t="s">
+        <v>43</v>
+      </c>
+      <c r="G129">
+        <v>7</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129" t="s">
+        <v>158</v>
+      </c>
+      <c r="J129">
+        <v>2125504</v>
+      </c>
+      <c r="K129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L129" t="str">
+        <f t="shared" si="1"/>
+        <v>穿搭博主游客的升星道具</v>
+      </c>
+      <c r="O129">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
+      <c r="A130">
+        <v>1125505</v>
+      </c>
+      <c r="C130">
+        <v>1125505</v>
+      </c>
+      <c r="D130" t="str">
+        <f t="shared" si="0"/>
+        <v>美妆新秀碎片</v>
+      </c>
+      <c r="E130">
+        <v>2</v>
+      </c>
+      <c r="F130" t="s">
+        <v>43</v>
+      </c>
+      <c r="G130">
+        <v>7</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130" t="s">
+        <v>158</v>
+      </c>
+      <c r="J130">
+        <v>2125505</v>
+      </c>
+      <c r="K130" t="b">
+        <v>0</v>
+      </c>
+      <c r="L130" t="str">
+        <f t="shared" si="1"/>
+        <v>美妆新秀游客的升星道具</v>
+      </c>
+      <c r="O130">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
+      <c r="A131">
+        <v>1125506</v>
+      </c>
+      <c r="C131">
+        <v>1125506</v>
+      </c>
+      <c r="D131" t="str">
+        <f t="shared" si="0"/>
+        <v>高定女王碎片</v>
+      </c>
+      <c r="E131">
+        <v>2</v>
+      </c>
+      <c r="F131" t="s">
+        <v>43</v>
+      </c>
+      <c r="G131">
+        <v>7</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131" t="s">
+        <v>158</v>
+      </c>
+      <c r="J131">
+        <v>2125506</v>
+      </c>
+      <c r="K131" t="b">
+        <v>0</v>
+      </c>
+      <c r="L131" t="str">
+        <f t="shared" si="1"/>
+        <v>高定女王游客的升星道具</v>
+      </c>
+      <c r="O131">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
+      <c r="A132">
+        <v>1026001</v>
+      </c>
+      <c r="C132">
+        <v>1026001</v>
+      </c>
+      <c r="D132" t="s">
+        <v>205</v>
+      </c>
+      <c r="E132">
+        <v>2</v>
+      </c>
+      <c r="F132" t="s">
+        <v>43</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+      <c r="I132" t="s">
+        <v>158</v>
+      </c>
+      <c r="J132">
+        <v>2026001</v>
+      </c>
+      <c r="K132" t="b">
+        <v>0</v>
+      </c>
+      <c r="L132" t="s">
+        <v>205</v>
+      </c>
+      <c r="O132">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
+      <c r="A133">
+        <v>1026002</v>
+      </c>
+      <c r="C133">
+        <v>1026002</v>
+      </c>
+      <c r="D133" t="s">
+        <v>206</v>
+      </c>
+      <c r="E133">
+        <v>2</v>
+      </c>
+      <c r="F133" t="s">
+        <v>43</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133" t="s">
+        <v>158</v>
+      </c>
+      <c r="J133">
+        <v>2026002</v>
+      </c>
+      <c r="K133" t="b">
+        <v>0</v>
+      </c>
+      <c r="L133" t="s">
+        <v>206</v>
+      </c>
+      <c r="O133">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
+      <c r="A134">
+        <v>1026101</v>
+      </c>
+      <c r="C134">
+        <v>1026101</v>
+      </c>
+      <c r="D134" t="s">
+        <v>207</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
+      <c r="F134" t="s">
+        <v>43</v>
+      </c>
+      <c r="G134">
+        <v>2</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134" t="s">
+        <v>158</v>
+      </c>
+      <c r="J134">
+        <v>2026101</v>
+      </c>
+      <c r="K134" t="b">
+        <v>0</v>
+      </c>
+      <c r="L134" t="s">
+        <v>207</v>
+      </c>
+      <c r="O134">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
+      <c r="A135">
+        <v>1026102</v>
+      </c>
+      <c r="C135">
+        <v>1026102</v>
+      </c>
+      <c r="D135" t="s">
+        <v>208</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
+      <c r="F135" t="s">
+        <v>43</v>
+      </c>
+      <c r="G135">
+        <v>2</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135" t="s">
+        <v>158</v>
+      </c>
+      <c r="J135">
+        <v>2026102</v>
+      </c>
+      <c r="K135" t="b">
+        <v>0</v>
+      </c>
+      <c r="L135" t="s">
+        <v>208</v>
+      </c>
+      <c r="O135">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
+      <c r="A136">
+        <v>1026201</v>
+      </c>
+      <c r="C136">
+        <v>1026201</v>
+      </c>
+      <c r="D136" t="s">
+        <v>209</v>
+      </c>
+      <c r="E136">
+        <v>2</v>
+      </c>
+      <c r="F136" t="s">
+        <v>43</v>
+      </c>
+      <c r="G136">
+        <v>3</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136" t="s">
+        <v>158</v>
+      </c>
+      <c r="J136">
+        <v>2026201</v>
+      </c>
+      <c r="K136" t="b">
+        <v>0</v>
+      </c>
+      <c r="L136" t="s">
+        <v>209</v>
+      </c>
+      <c r="O136">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
+      <c r="A137">
+        <v>1026202</v>
+      </c>
+      <c r="C137">
+        <v>1026202</v>
+      </c>
+      <c r="D137" t="s">
+        <v>210</v>
+      </c>
+      <c r="E137">
+        <v>2</v>
+      </c>
+      <c r="F137" t="s">
+        <v>43</v>
+      </c>
+      <c r="G137">
+        <v>3</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137" t="s">
+        <v>158</v>
+      </c>
+      <c r="J137">
+        <v>2026202</v>
+      </c>
+      <c r="K137" t="b">
+        <v>0</v>
+      </c>
+      <c r="L137" t="s">
+        <v>210</v>
+      </c>
+      <c r="O137">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
+      <c r="A138">
+        <v>1026301</v>
+      </c>
+      <c r="C138">
+        <v>1026301</v>
+      </c>
+      <c r="D138" t="s">
+        <v>211</v>
+      </c>
+      <c r="E138">
+        <v>2</v>
+      </c>
+      <c r="F138" t="s">
+        <v>43</v>
+      </c>
+      <c r="G138">
+        <v>4</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138" t="s">
+        <v>158</v>
+      </c>
+      <c r="J138">
+        <v>2026301</v>
+      </c>
+      <c r="K138" t="b">
+        <v>0</v>
+      </c>
+      <c r="L138" t="s">
+        <v>211</v>
+      </c>
+      <c r="O138">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
+      <c r="A139">
+        <v>1026302</v>
+      </c>
+      <c r="C139">
+        <v>1026302</v>
+      </c>
+      <c r="D139" t="s">
+        <v>212</v>
+      </c>
+      <c r="E139">
+        <v>2</v>
+      </c>
+      <c r="F139" t="s">
+        <v>43</v>
+      </c>
+      <c r="G139">
+        <v>4</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139" t="s">
+        <v>158</v>
+      </c>
+      <c r="J139">
+        <v>2026302</v>
+      </c>
+      <c r="K139" t="b">
+        <v>0</v>
+      </c>
+      <c r="L139" t="s">
+        <v>212</v>
+      </c>
+      <c r="O139">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
+      <c r="A140">
+        <v>1026401</v>
+      </c>
+      <c r="C140">
+        <v>1026401</v>
+      </c>
+      <c r="D140" t="s">
+        <v>213</v>
+      </c>
+      <c r="E140">
+        <v>2</v>
+      </c>
+      <c r="F140" t="s">
+        <v>43</v>
+      </c>
+      <c r="G140">
+        <v>7</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140" t="s">
+        <v>158</v>
+      </c>
+      <c r="J140">
+        <v>2026401</v>
+      </c>
+      <c r="K140" t="b">
+        <v>0</v>
+      </c>
+      <c r="L140" t="s">
+        <v>213</v>
+      </c>
+      <c r="O140">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
+      <c r="A141">
+        <v>1026402</v>
+      </c>
+      <c r="C141">
+        <v>1026402</v>
+      </c>
+      <c r="D141" t="s">
+        <v>214</v>
+      </c>
+      <c r="E141">
+        <v>2</v>
+      </c>
+      <c r="F141" t="s">
+        <v>43</v>
+      </c>
+      <c r="G141">
+        <v>7</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141" t="s">
+        <v>158</v>
+      </c>
+      <c r="J141">
+        <v>2026402</v>
+      </c>
+      <c r="K141" t="b">
+        <v>0</v>
+      </c>
+      <c r="L141" t="s">
+        <v>214</v>
+      </c>
+      <c r="O141">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
+      <c r="A142">
+        <v>1027001</v>
+      </c>
+      <c r="C142">
+        <v>1027001</v>
+      </c>
+      <c r="D142" t="s">
+        <v>215</v>
+      </c>
+      <c r="E142">
+        <v>2</v>
+      </c>
+      <c r="F142" t="s">
+        <v>43</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="I142" t="s">
+        <v>158</v>
+      </c>
+      <c r="J142">
+        <v>2027001</v>
+      </c>
+      <c r="K142" t="b">
+        <v>0</v>
+      </c>
+      <c r="L142" t="s">
+        <v>215</v>
+      </c>
+      <c r="O142">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15">
+      <c r="A143">
+        <v>1027002</v>
+      </c>
+      <c r="C143">
+        <v>1027002</v>
+      </c>
+      <c r="D143" t="s">
+        <v>216</v>
+      </c>
+      <c r="E143">
+        <v>2</v>
+      </c>
+      <c r="F143" t="s">
+        <v>43</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143" t="s">
+        <v>158</v>
+      </c>
+      <c r="J143">
+        <v>2027002</v>
+      </c>
+      <c r="K143" t="b">
+        <v>0</v>
+      </c>
+      <c r="L143" t="s">
+        <v>216</v>
+      </c>
+      <c r="O143">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15">
+      <c r="A144">
+        <v>1027101</v>
+      </c>
+      <c r="C144">
+        <v>1027101</v>
+      </c>
+      <c r="D144" t="s">
+        <v>217</v>
+      </c>
+      <c r="E144">
+        <v>2</v>
+      </c>
+      <c r="F144" t="s">
+        <v>43</v>
+      </c>
+      <c r="G144">
+        <v>2</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+      <c r="I144" t="s">
+        <v>158</v>
+      </c>
+      <c r="J144">
+        <v>2027101</v>
+      </c>
+      <c r="K144" t="b">
+        <v>0</v>
+      </c>
+      <c r="L144" t="s">
+        <v>217</v>
+      </c>
+      <c r="O144">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
+      <c r="A145">
+        <v>1027102</v>
+      </c>
+      <c r="C145">
+        <v>1027102</v>
+      </c>
+      <c r="D145" t="s">
+        <v>218</v>
+      </c>
+      <c r="E145">
+        <v>2</v>
+      </c>
+      <c r="F145" t="s">
+        <v>43</v>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="I145" t="s">
+        <v>158</v>
+      </c>
+      <c r="J145">
+        <v>2027102</v>
+      </c>
+      <c r="K145" t="b">
+        <v>0</v>
+      </c>
+      <c r="L145" t="s">
+        <v>218</v>
+      </c>
+      <c r="O145">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
+      <c r="A146">
+        <v>1027201</v>
+      </c>
+      <c r="C146">
+        <v>1027201</v>
+      </c>
+      <c r="D146" t="s">
+        <v>219</v>
+      </c>
+      <c r="E146">
+        <v>2</v>
+      </c>
+      <c r="F146" t="s">
+        <v>43</v>
+      </c>
+      <c r="G146">
+        <v>3</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+      <c r="I146" t="s">
+        <v>158</v>
+      </c>
+      <c r="J146">
+        <v>2027201</v>
+      </c>
+      <c r="K146" t="b">
+        <v>0</v>
+      </c>
+      <c r="L146" t="s">
+        <v>219</v>
+      </c>
+      <c r="O146">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
+      <c r="A147">
+        <v>1027202</v>
+      </c>
+      <c r="C147">
+        <v>1027202</v>
+      </c>
+      <c r="D147" t="s">
+        <v>220</v>
+      </c>
+      <c r="E147">
+        <v>2</v>
+      </c>
+      <c r="F147" t="s">
+        <v>43</v>
+      </c>
+      <c r="G147">
+        <v>3</v>
+      </c>
+      <c r="H147">
+        <v>1</v>
+      </c>
+      <c r="I147" t="s">
+        <v>158</v>
+      </c>
+      <c r="J147">
+        <v>2027202</v>
+      </c>
+      <c r="K147" t="b">
+        <v>0</v>
+      </c>
+      <c r="L147" t="s">
+        <v>220</v>
+      </c>
+      <c r="O147">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15">
+      <c r="A148">
+        <v>1027301</v>
+      </c>
+      <c r="C148">
+        <v>1027301</v>
+      </c>
+      <c r="D148" t="s">
+        <v>221</v>
+      </c>
+      <c r="E148">
+        <v>2</v>
+      </c>
+      <c r="F148" t="s">
+        <v>43</v>
+      </c>
+      <c r="G148">
+        <v>4</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+      <c r="I148" t="s">
+        <v>158</v>
+      </c>
+      <c r="J148">
+        <v>2027301</v>
+      </c>
+      <c r="K148" t="b">
+        <v>0</v>
+      </c>
+      <c r="L148" t="s">
+        <v>221</v>
+      </c>
+      <c r="O148">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
+      <c r="A149">
+        <v>1027302</v>
+      </c>
+      <c r="C149">
+        <v>1027302</v>
+      </c>
+      <c r="D149" t="s">
+        <v>222</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+      <c r="F149" t="s">
+        <v>43</v>
+      </c>
+      <c r="G149">
+        <v>4</v>
+      </c>
+      <c r="H149">
+        <v>1</v>
+      </c>
+      <c r="I149" t="s">
+        <v>158</v>
+      </c>
+      <c r="J149">
+        <v>2027302</v>
+      </c>
+      <c r="K149" t="b">
+        <v>0</v>
+      </c>
+      <c r="L149" t="s">
+        <v>222</v>
+      </c>
+      <c r="O149">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
+      <c r="A150">
+        <v>1027401</v>
+      </c>
+      <c r="C150">
+        <v>1027401</v>
+      </c>
+      <c r="D150" t="s">
+        <v>223</v>
+      </c>
+      <c r="E150">
+        <v>2</v>
+      </c>
+      <c r="F150" t="s">
+        <v>43</v>
+      </c>
+      <c r="G150">
+        <v>7</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150" t="s">
+        <v>158</v>
+      </c>
+      <c r="J150">
+        <v>2027401</v>
+      </c>
+      <c r="K150" t="b">
+        <v>0</v>
+      </c>
+      <c r="L150" t="s">
+        <v>223</v>
+      </c>
+      <c r="O150">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15">
+      <c r="A151">
+        <v>1027402</v>
+      </c>
+      <c r="C151">
+        <v>1027402</v>
+      </c>
+      <c r="D151" t="s">
+        <v>224</v>
+      </c>
+      <c r="E151">
+        <v>2</v>
+      </c>
+      <c r="F151" t="s">
+        <v>43</v>
+      </c>
+      <c r="G151">
+        <v>7</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151" t="s">
+        <v>158</v>
+      </c>
+      <c r="J151">
+        <v>2027402</v>
+      </c>
+      <c r="K151" t="b">
+        <v>0</v>
+      </c>
+      <c r="L151" t="s">
+        <v>224</v>
+      </c>
+      <c r="O151">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
+      <c r="A152">
+        <v>1028001</v>
+      </c>
+      <c r="C152">
+        <v>1028001</v>
+      </c>
+      <c r="D152" t="s">
+        <v>225</v>
+      </c>
+      <c r="E152">
+        <v>2</v>
+      </c>
+      <c r="F152" t="s">
+        <v>43</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="I152" t="s">
+        <v>158</v>
+      </c>
+      <c r="J152">
+        <v>2028001</v>
+      </c>
+      <c r="K152" t="b">
+        <v>0</v>
+      </c>
+      <c r="L152" t="s">
+        <v>225</v>
+      </c>
+      <c r="O152">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
+      <c r="A153">
+        <v>1028002</v>
+      </c>
+      <c r="C153">
+        <v>1028002</v>
+      </c>
+      <c r="D153" t="s">
+        <v>226</v>
+      </c>
+      <c r="E153">
+        <v>2</v>
+      </c>
+      <c r="F153" t="s">
+        <v>43</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+      <c r="H153">
+        <v>1</v>
+      </c>
+      <c r="I153" t="s">
+        <v>158</v>
+      </c>
+      <c r="J153">
+        <v>2028002</v>
+      </c>
+      <c r="K153" t="b">
+        <v>0</v>
+      </c>
+      <c r="L153" t="s">
+        <v>226</v>
+      </c>
+      <c r="O153">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15">
+      <c r="A154">
+        <v>1028101</v>
+      </c>
+      <c r="C154">
+        <v>1028101</v>
+      </c>
+      <c r="D154" t="s">
+        <v>227</v>
+      </c>
+      <c r="E154">
+        <v>2</v>
+      </c>
+      <c r="F154" t="s">
+        <v>43</v>
+      </c>
+      <c r="G154">
+        <v>2</v>
+      </c>
+      <c r="H154">
+        <v>1</v>
+      </c>
+      <c r="I154" t="s">
+        <v>158</v>
+      </c>
+      <c r="J154">
+        <v>2028101</v>
+      </c>
+      <c r="K154" t="b">
+        <v>0</v>
+      </c>
+      <c r="L154" t="s">
+        <v>227</v>
+      </c>
+      <c r="O154">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15">
+      <c r="A155">
+        <v>1028102</v>
+      </c>
+      <c r="C155">
+        <v>1028102</v>
+      </c>
+      <c r="D155" t="s">
+        <v>228</v>
+      </c>
+      <c r="E155">
+        <v>2</v>
+      </c>
+      <c r="F155" t="s">
+        <v>43</v>
+      </c>
+      <c r="G155">
+        <v>2</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+      <c r="I155" t="s">
+        <v>158</v>
+      </c>
+      <c r="J155">
+        <v>2028102</v>
+      </c>
+      <c r="K155" t="b">
+        <v>0</v>
+      </c>
+      <c r="L155" t="s">
+        <v>228</v>
+      </c>
+      <c r="O155">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15">
+      <c r="A156">
+        <v>1028201</v>
+      </c>
+      <c r="C156">
+        <v>1028201</v>
+      </c>
+      <c r="D156" t="s">
+        <v>229</v>
+      </c>
+      <c r="E156">
+        <v>2</v>
+      </c>
+      <c r="F156" t="s">
+        <v>43</v>
+      </c>
+      <c r="G156">
+        <v>3</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+      <c r="I156" t="s">
+        <v>158</v>
+      </c>
+      <c r="J156">
+        <v>2028201</v>
+      </c>
+      <c r="K156" t="b">
+        <v>0</v>
+      </c>
+      <c r="L156" t="s">
+        <v>229</v>
+      </c>
+      <c r="O156">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
+      <c r="A157">
+        <v>1028202</v>
+      </c>
+      <c r="C157">
+        <v>1028202</v>
+      </c>
+      <c r="D157" t="s">
+        <v>230</v>
+      </c>
+      <c r="E157">
+        <v>2</v>
+      </c>
+      <c r="F157" t="s">
+        <v>43</v>
+      </c>
+      <c r="G157">
+        <v>3</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="I157" t="s">
+        <v>158</v>
+      </c>
+      <c r="J157">
+        <v>2028202</v>
+      </c>
+      <c r="K157" t="b">
+        <v>0</v>
+      </c>
+      <c r="L157" t="s">
+        <v>230</v>
+      </c>
+      <c r="O157">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15">
+      <c r="A158">
+        <v>1028301</v>
+      </c>
+      <c r="C158">
+        <v>1028301</v>
+      </c>
+      <c r="D158" t="s">
+        <v>231</v>
+      </c>
+      <c r="E158">
+        <v>2</v>
+      </c>
+      <c r="F158" t="s">
+        <v>43</v>
+      </c>
+      <c r="G158">
+        <v>4</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+      <c r="I158" t="s">
+        <v>158</v>
+      </c>
+      <c r="J158">
+        <v>2028301</v>
+      </c>
+      <c r="K158" t="b">
+        <v>0</v>
+      </c>
+      <c r="L158" t="s">
+        <v>231</v>
+      </c>
+      <c r="O158">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
+      <c r="A159">
+        <v>1028302</v>
+      </c>
+      <c r="C159">
+        <v>1028302</v>
+      </c>
+      <c r="D159" t="s">
+        <v>232</v>
+      </c>
+      <c r="E159">
+        <v>2</v>
+      </c>
+      <c r="F159" t="s">
+        <v>43</v>
+      </c>
+      <c r="G159">
+        <v>4</v>
+      </c>
+      <c r="H159">
+        <v>1</v>
+      </c>
+      <c r="I159" t="s">
+        <v>158</v>
+      </c>
+      <c r="J159">
+        <v>2028302</v>
+      </c>
+      <c r="K159" t="b">
+        <v>0</v>
+      </c>
+      <c r="L159" t="s">
+        <v>232</v>
+      </c>
+      <c r="O159">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
+      <c r="A160">
+        <v>1028401</v>
+      </c>
+      <c r="C160">
+        <v>1028401</v>
+      </c>
+      <c r="D160" t="s">
+        <v>233</v>
+      </c>
+      <c r="E160">
+        <v>2</v>
+      </c>
+      <c r="F160" t="s">
+        <v>43</v>
+      </c>
+      <c r="G160">
+        <v>7</v>
+      </c>
+      <c r="H160">
+        <v>1</v>
+      </c>
+      <c r="I160" t="s">
+        <v>158</v>
+      </c>
+      <c r="J160">
+        <v>2028401</v>
+      </c>
+      <c r="K160" t="b">
+        <v>0</v>
+      </c>
+      <c r="L160" t="s">
+        <v>233</v>
+      </c>
+      <c r="O160">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
+      <c r="A161">
+        <v>1028402</v>
+      </c>
+      <c r="C161">
+        <v>1028402</v>
+      </c>
+      <c r="D161" t="s">
+        <v>234</v>
+      </c>
+      <c r="E161">
+        <v>2</v>
+      </c>
+      <c r="F161" t="s">
+        <v>43</v>
+      </c>
+      <c r="G161">
+        <v>7</v>
+      </c>
+      <c r="H161">
+        <v>1</v>
+      </c>
+      <c r="I161" t="s">
+        <v>158</v>
+      </c>
+      <c r="J161">
+        <v>2028402</v>
+      </c>
+      <c r="K161" t="b">
+        <v>0</v>
+      </c>
+      <c r="L161" t="s">
+        <v>234</v>
+      </c>
+      <c r="O161">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15">
+      <c r="A162">
+        <v>1126001</v>
+      </c>
+      <c r="C162">
+        <v>1126001</v>
+      </c>
+      <c r="D162" t="str">
+        <f>D132&amp;"碎片"</f>
+        <v>威廉碎片</v>
+      </c>
+      <c r="E162">
+        <v>2</v>
+      </c>
+      <c r="F162" t="s">
+        <v>43</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+      <c r="H162">
+        <v>1</v>
+      </c>
+      <c r="I162" t="s">
+        <v>158</v>
+      </c>
+      <c r="J162">
+        <v>2126001</v>
+      </c>
+      <c r="K162" t="b">
+        <v>0</v>
+      </c>
+      <c r="L162" t="str">
+        <f>D132&amp;"雇员的升星道具"</f>
+        <v>威廉雇员的升星道具</v>
+      </c>
+      <c r="O162">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
+      <c r="A163">
+        <v>1126002</v>
+      </c>
+      <c r="C163">
+        <v>1126002</v>
+      </c>
+      <c r="D163" t="str">
+        <f t="shared" ref="D163:D191" si="2">D133&amp;"碎片"</f>
+        <v>艾拉碎片</v>
+      </c>
+      <c r="E163">
+        <v>2</v>
+      </c>
+      <c r="F163" t="s">
+        <v>43</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163">
+        <v>1</v>
+      </c>
+      <c r="I163" t="s">
+        <v>158</v>
+      </c>
+      <c r="J163">
+        <v>2126002</v>
+      </c>
+      <c r="K163" t="b">
+        <v>0</v>
+      </c>
+      <c r="L163" t="str">
+        <f t="shared" ref="L163:L191" si="3">D133&amp;"雇员的升星道具"</f>
+        <v>艾拉雇员的升星道具</v>
+      </c>
+      <c r="O163">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
+      <c r="A164">
+        <v>1126101</v>
+      </c>
+      <c r="C164">
+        <v>1126101</v>
+      </c>
+      <c r="D164" t="str">
+        <f t="shared" si="2"/>
+        <v>亨利碎片</v>
+      </c>
+      <c r="E164">
+        <v>2</v>
+      </c>
+      <c r="F164" t="s">
+        <v>43</v>
+      </c>
+      <c r="G164">
+        <v>2</v>
+      </c>
+      <c r="H164">
+        <v>1</v>
+      </c>
+      <c r="I164" t="s">
+        <v>158</v>
+      </c>
+      <c r="J164">
+        <v>2126101</v>
+      </c>
+      <c r="K164" t="b">
+        <v>0</v>
+      </c>
+      <c r="L164" t="str">
+        <f t="shared" si="3"/>
+        <v>亨利雇员的升星道具</v>
+      </c>
+      <c r="O164">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
+      <c r="A165">
+        <v>1126102</v>
+      </c>
+      <c r="C165">
+        <v>1126102</v>
+      </c>
+      <c r="D165" t="str">
+        <f t="shared" si="2"/>
+        <v>艾玛碎片</v>
+      </c>
+      <c r="E165">
+        <v>2</v>
+      </c>
+      <c r="F165" t="s">
+        <v>43</v>
+      </c>
+      <c r="G165">
+        <v>2</v>
+      </c>
+      <c r="H165">
+        <v>1</v>
+      </c>
+      <c r="I165" t="s">
+        <v>158</v>
+      </c>
+      <c r="J165">
+        <v>2126102</v>
+      </c>
+      <c r="K165" t="b">
+        <v>0</v>
+      </c>
+      <c r="L165" t="str">
+        <f t="shared" si="3"/>
+        <v>艾玛雇员的升星道具</v>
+      </c>
+      <c r="O165">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15">
+      <c r="A166">
+        <v>1126201</v>
+      </c>
+      <c r="C166">
+        <v>1126201</v>
+      </c>
+      <c r="D166" t="str">
+        <f t="shared" si="2"/>
+        <v>乔治碎片</v>
+      </c>
+      <c r="E166">
+        <v>2</v>
+      </c>
+      <c r="F166" t="s">
+        <v>43</v>
+      </c>
+      <c r="G166">
+        <v>3</v>
+      </c>
+      <c r="H166">
+        <v>1</v>
+      </c>
+      <c r="I166" t="s">
+        <v>158</v>
+      </c>
+      <c r="J166">
+        <v>2126201</v>
+      </c>
+      <c r="K166" t="b">
+        <v>0</v>
+      </c>
+      <c r="L166" t="str">
+        <f t="shared" si="3"/>
+        <v>乔治雇员的升星道具</v>
+      </c>
+      <c r="O166">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15">
+      <c r="A167">
+        <v>1126202</v>
+      </c>
+      <c r="C167">
+        <v>1126202</v>
+      </c>
+      <c r="D167" t="str">
+        <f t="shared" si="2"/>
+        <v>艾娃碎片</v>
+      </c>
+      <c r="E167">
+        <v>2</v>
+      </c>
+      <c r="F167" t="s">
+        <v>43</v>
+      </c>
+      <c r="G167">
+        <v>3</v>
+      </c>
+      <c r="H167">
+        <v>1</v>
+      </c>
+      <c r="I167" t="s">
+        <v>158</v>
+      </c>
+      <c r="J167">
+        <v>2126202</v>
+      </c>
+      <c r="K167" t="b">
+        <v>0</v>
+      </c>
+      <c r="L167" t="str">
+        <f t="shared" si="3"/>
+        <v>艾娃雇员的升星道具</v>
+      </c>
+      <c r="O167">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15">
+      <c r="A168">
+        <v>1126301</v>
+      </c>
+      <c r="C168">
+        <v>1126301</v>
+      </c>
+      <c r="D168" t="str">
+        <f t="shared" si="2"/>
+        <v>亚瑟碎片</v>
+      </c>
+      <c r="E168">
+        <v>2</v>
+      </c>
+      <c r="F168" t="s">
+        <v>43</v>
+      </c>
+      <c r="G168">
+        <v>4</v>
+      </c>
+      <c r="H168">
+        <v>1</v>
+      </c>
+      <c r="I168" t="s">
+        <v>158</v>
+      </c>
+      <c r="J168">
+        <v>2126301</v>
+      </c>
+      <c r="K168" t="b">
+        <v>0</v>
+      </c>
+      <c r="L168" t="str">
+        <f t="shared" si="3"/>
+        <v>亚瑟雇员的升星道具</v>
+      </c>
+      <c r="O168">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15">
+      <c r="A169">
+        <v>1126302</v>
+      </c>
+      <c r="C169">
+        <v>1126302</v>
+      </c>
+      <c r="D169" t="str">
+        <f t="shared" si="2"/>
+        <v>安娜碎片</v>
+      </c>
+      <c r="E169">
+        <v>2</v>
+      </c>
+      <c r="F169" t="s">
+        <v>43</v>
+      </c>
+      <c r="G169">
+        <v>4</v>
+      </c>
+      <c r="H169">
+        <v>1</v>
+      </c>
+      <c r="I169" t="s">
+        <v>158</v>
+      </c>
+      <c r="J169">
+        <v>2126302</v>
+      </c>
+      <c r="K169" t="b">
+        <v>0</v>
+      </c>
+      <c r="L169" t="str">
+        <f t="shared" si="3"/>
+        <v>安娜雇员的升星道具</v>
+      </c>
+      <c r="O169">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15">
+      <c r="A170">
+        <v>1126401</v>
+      </c>
+      <c r="C170">
+        <v>1126401</v>
+      </c>
+      <c r="D170" t="str">
+        <f t="shared" si="2"/>
+        <v>马修碎片</v>
+      </c>
+      <c r="E170">
+        <v>2</v>
+      </c>
+      <c r="F170" t="s">
+        <v>43</v>
+      </c>
+      <c r="G170">
+        <v>7</v>
+      </c>
+      <c r="H170">
+        <v>1</v>
+      </c>
+      <c r="I170" t="s">
+        <v>158</v>
+      </c>
+      <c r="J170">
+        <v>2126401</v>
+      </c>
+      <c r="K170" t="b">
+        <v>0</v>
+      </c>
+      <c r="L170" t="str">
+        <f t="shared" si="3"/>
+        <v>马修雇员的升星道具</v>
+      </c>
+      <c r="O170">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15">
+      <c r="A171">
+        <v>1126402</v>
+      </c>
+      <c r="C171">
+        <v>1126402</v>
+      </c>
+      <c r="D171" t="str">
+        <f t="shared" si="2"/>
+        <v>哈珀碎片</v>
+      </c>
+      <c r="E171">
+        <v>2</v>
+      </c>
+      <c r="F171" t="s">
+        <v>43</v>
+      </c>
+      <c r="G171">
+        <v>7</v>
+      </c>
+      <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="I171" t="s">
+        <v>158</v>
+      </c>
+      <c r="J171">
+        <v>2126402</v>
+      </c>
+      <c r="K171" t="b">
+        <v>0</v>
+      </c>
+      <c r="L171" t="str">
+        <f t="shared" si="3"/>
+        <v>哈珀雇员的升星道具</v>
+      </c>
+      <c r="O171">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15">
+      <c r="A172">
+        <v>1127001</v>
+      </c>
+      <c r="C172">
+        <v>1127001</v>
+      </c>
+      <c r="D172" t="str">
+        <f t="shared" si="2"/>
+        <v>拉斐尔碎片</v>
+      </c>
+      <c r="E172">
+        <v>2</v>
+      </c>
+      <c r="F172" t="s">
+        <v>43</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172">
+        <v>1</v>
+      </c>
+      <c r="I172" t="s">
+        <v>158</v>
+      </c>
+      <c r="J172">
+        <v>2127001</v>
+      </c>
+      <c r="K172" t="b">
+        <v>0</v>
+      </c>
+      <c r="L172" t="str">
+        <f t="shared" si="3"/>
+        <v>拉斐尔雇员的升星道具</v>
+      </c>
+      <c r="O172">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15">
+      <c r="A173">
+        <v>1127002</v>
+      </c>
+      <c r="C173">
+        <v>1127002</v>
+      </c>
+      <c r="D173" t="str">
+        <f t="shared" si="2"/>
+        <v>伊芙琳碎片</v>
+      </c>
+      <c r="E173">
+        <v>2</v>
+      </c>
+      <c r="F173" t="s">
+        <v>43</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>1</v>
+      </c>
+      <c r="I173" t="s">
+        <v>158</v>
+      </c>
+      <c r="J173">
+        <v>2127002</v>
+      </c>
+      <c r="K173" t="b">
+        <v>0</v>
+      </c>
+      <c r="L173" t="str">
+        <f t="shared" si="3"/>
+        <v>伊芙琳雇员的升星道具</v>
+      </c>
+      <c r="O173">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15">
+      <c r="A174">
+        <v>1127101</v>
+      </c>
+      <c r="C174">
+        <v>1127101</v>
+      </c>
+      <c r="D174" t="str">
+        <f t="shared" si="2"/>
+        <v>埃米尔碎片</v>
+      </c>
+      <c r="E174">
+        <v>2</v>
+      </c>
+      <c r="F174" t="s">
+        <v>43</v>
+      </c>
+      <c r="G174">
+        <v>2</v>
+      </c>
+      <c r="H174">
+        <v>1</v>
+      </c>
+      <c r="I174" t="s">
+        <v>158</v>
+      </c>
+      <c r="J174">
+        <v>2127101</v>
+      </c>
+      <c r="K174" t="b">
+        <v>0</v>
+      </c>
+      <c r="L174" t="str">
+        <f t="shared" si="3"/>
+        <v>埃米尔雇员的升星道具</v>
+      </c>
+      <c r="O174">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15">
+      <c r="A175">
+        <v>1127102</v>
+      </c>
+      <c r="C175">
+        <v>1127102</v>
+      </c>
+      <c r="D175" t="str">
+        <f t="shared" si="2"/>
+        <v>夏洛特碎片</v>
+      </c>
+      <c r="E175">
+        <v>2</v>
+      </c>
+      <c r="F175" t="s">
+        <v>43</v>
+      </c>
+      <c r="G175">
+        <v>2</v>
+      </c>
+      <c r="H175">
+        <v>1</v>
+      </c>
+      <c r="I175" t="s">
+        <v>158</v>
+      </c>
+      <c r="J175">
+        <v>2127102</v>
+      </c>
+      <c r="K175" t="b">
+        <v>0</v>
+      </c>
+      <c r="L175" t="str">
+        <f t="shared" si="3"/>
+        <v>夏洛特雇员的升星道具</v>
+      </c>
+      <c r="O175">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15">
+      <c r="A176">
+        <v>1127201</v>
+      </c>
+      <c r="C176">
+        <v>1127201</v>
+      </c>
+      <c r="D176" t="str">
+        <f t="shared" si="2"/>
+        <v>雷蒙德碎片</v>
+      </c>
+      <c r="E176">
+        <v>2</v>
+      </c>
+      <c r="F176" t="s">
+        <v>43</v>
+      </c>
+      <c r="G176">
+        <v>3</v>
+      </c>
+      <c r="H176">
+        <v>1</v>
+      </c>
+      <c r="I176" t="s">
+        <v>158</v>
+      </c>
+      <c r="J176">
+        <v>2127201</v>
+      </c>
+      <c r="K176" t="b">
+        <v>0</v>
+      </c>
+      <c r="L176" t="str">
+        <f t="shared" si="3"/>
+        <v>雷蒙德雇员的升星道具</v>
+      </c>
+      <c r="O176">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
+      <c r="A177">
+        <v>1127202</v>
+      </c>
+      <c r="C177">
+        <v>1127202</v>
+      </c>
+      <c r="D177" t="str">
+        <f t="shared" si="2"/>
+        <v>斯嘉丽碎片</v>
+      </c>
+      <c r="E177">
+        <v>2</v>
+      </c>
+      <c r="F177" t="s">
+        <v>43</v>
+      </c>
+      <c r="G177">
+        <v>3</v>
+      </c>
+      <c r="H177">
+        <v>1</v>
+      </c>
+      <c r="I177" t="s">
+        <v>158</v>
+      </c>
+      <c r="J177">
+        <v>2127202</v>
+      </c>
+      <c r="K177" t="b">
+        <v>0</v>
+      </c>
+      <c r="L177" t="str">
+        <f t="shared" si="3"/>
+        <v>斯嘉丽雇员的升星道具</v>
+      </c>
+      <c r="O177">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15">
+      <c r="A178">
+        <v>1127301</v>
+      </c>
+      <c r="C178">
+        <v>1127301</v>
+      </c>
+      <c r="D178" t="str">
+        <f t="shared" si="2"/>
+        <v>丹尼尔碎片</v>
+      </c>
+      <c r="E178">
+        <v>2</v>
+      </c>
+      <c r="F178" t="s">
+        <v>43</v>
+      </c>
+      <c r="G178">
+        <v>4</v>
+      </c>
+      <c r="H178">
+        <v>1</v>
+      </c>
+      <c r="I178" t="s">
+        <v>158</v>
+      </c>
+      <c r="J178">
+        <v>2127301</v>
+      </c>
+      <c r="K178" t="b">
+        <v>0</v>
+      </c>
+      <c r="L178" t="str">
+        <f t="shared" si="3"/>
+        <v>丹尼尔雇员的升星道具</v>
+      </c>
+      <c r="O178">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15">
+      <c r="A179">
+        <v>1127302</v>
+      </c>
+      <c r="C179">
+        <v>1127302</v>
+      </c>
+      <c r="D179" t="str">
+        <f t="shared" si="2"/>
+        <v>莉莉安碎片</v>
+      </c>
+      <c r="E179">
+        <v>2</v>
+      </c>
+      <c r="F179" t="s">
+        <v>43</v>
+      </c>
+      <c r="G179">
+        <v>4</v>
+      </c>
+      <c r="H179">
+        <v>1</v>
+      </c>
+      <c r="I179" t="s">
+        <v>158</v>
+      </c>
+      <c r="J179">
+        <v>2127302</v>
+      </c>
+      <c r="K179" t="b">
+        <v>0</v>
+      </c>
+      <c r="L179" t="str">
+        <f t="shared" si="3"/>
+        <v>莉莉安雇员的升星道具</v>
+      </c>
+      <c r="O179">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15">
+      <c r="A180">
+        <v>1127401</v>
+      </c>
+      <c r="C180">
+        <v>1127401</v>
+      </c>
+      <c r="D180" t="str">
+        <f t="shared" si="2"/>
+        <v>卢卡斯碎片</v>
+      </c>
+      <c r="E180">
+        <v>2</v>
+      </c>
+      <c r="F180" t="s">
+        <v>43</v>
+      </c>
+      <c r="G180">
+        <v>7</v>
+      </c>
+      <c r="H180">
+        <v>1</v>
+      </c>
+      <c r="I180" t="s">
+        <v>158</v>
+      </c>
+      <c r="J180">
+        <v>2127401</v>
+      </c>
+      <c r="K180" t="b">
+        <v>0</v>
+      </c>
+      <c r="L180" t="str">
+        <f t="shared" si="3"/>
+        <v>卢卡斯雇员的升星道具</v>
+      </c>
+      <c r="O180">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15">
+      <c r="A181">
+        <v>1127402</v>
+      </c>
+      <c r="C181">
+        <v>1127402</v>
+      </c>
+      <c r="D181" t="str">
+        <f t="shared" si="2"/>
+        <v>克拉拉碎片</v>
+      </c>
+      <c r="E181">
+        <v>2</v>
+      </c>
+      <c r="F181" t="s">
+        <v>43</v>
+      </c>
+      <c r="G181">
+        <v>7</v>
+      </c>
+      <c r="H181">
+        <v>1</v>
+      </c>
+      <c r="I181" t="s">
+        <v>158</v>
+      </c>
+      <c r="J181">
+        <v>2127402</v>
+      </c>
+      <c r="K181" t="b">
+        <v>0</v>
+      </c>
+      <c r="L181" t="str">
+        <f t="shared" si="3"/>
+        <v>克拉拉雇员的升星道具</v>
+      </c>
+      <c r="O181">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15">
+      <c r="A182">
+        <v>1128001</v>
+      </c>
+      <c r="C182">
+        <v>1128001</v>
+      </c>
+      <c r="D182" t="str">
+        <f t="shared" si="2"/>
+        <v>尼古拉斯碎片</v>
+      </c>
+      <c r="E182">
+        <v>2</v>
+      </c>
+      <c r="F182" t="s">
+        <v>43</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+      <c r="H182">
+        <v>1</v>
+      </c>
+      <c r="I182" t="s">
+        <v>158</v>
+      </c>
+      <c r="J182">
+        <v>2128001</v>
+      </c>
+      <c r="K182" t="b">
+        <v>0</v>
+      </c>
+      <c r="L182" t="str">
+        <f t="shared" si="3"/>
+        <v>尼古拉斯雇员的升星道具</v>
+      </c>
+      <c r="O182">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15">
+      <c r="A183">
+        <v>1128002</v>
+      </c>
+      <c r="C183">
+        <v>1128002</v>
+      </c>
+      <c r="D183" t="str">
+        <f t="shared" si="2"/>
+        <v>奥利维亚碎片</v>
+      </c>
+      <c r="E183">
+        <v>2</v>
+      </c>
+      <c r="F183" t="s">
+        <v>43</v>
+      </c>
+      <c r="G183">
+        <v>1</v>
+      </c>
+      <c r="H183">
+        <v>1</v>
+      </c>
+      <c r="I183" t="s">
+        <v>158</v>
+      </c>
+      <c r="J183">
+        <v>2128002</v>
+      </c>
+      <c r="K183" t="b">
+        <v>0</v>
+      </c>
+      <c r="L183" t="str">
+        <f t="shared" si="3"/>
+        <v>奥利维亚雇员的升星道具</v>
+      </c>
+      <c r="O183">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15">
+      <c r="A184">
+        <v>1128101</v>
+      </c>
+      <c r="C184">
+        <v>1128101</v>
+      </c>
+      <c r="D184" t="str">
+        <f t="shared" si="2"/>
+        <v>亚历山大碎片</v>
+      </c>
+      <c r="E184">
+        <v>2</v>
+      </c>
+      <c r="F184" t="s">
+        <v>43</v>
+      </c>
+      <c r="G184">
+        <v>2</v>
+      </c>
+      <c r="H184">
+        <v>1</v>
+      </c>
+      <c r="I184" t="s">
+        <v>158</v>
+      </c>
+      <c r="J184">
+        <v>2128101</v>
+      </c>
+      <c r="K184" t="b">
+        <v>0</v>
+      </c>
+      <c r="L184" t="str">
+        <f t="shared" si="3"/>
+        <v>亚历山大雇员的升星道具</v>
+      </c>
+      <c r="O184">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15">
+      <c r="A185">
+        <v>1128102</v>
+      </c>
+      <c r="C185">
+        <v>1128102</v>
+      </c>
+      <c r="D185" t="str">
+        <f t="shared" si="2"/>
+        <v>玛格丽特碎片</v>
+      </c>
+      <c r="E185">
+        <v>2</v>
+      </c>
+      <c r="F185" t="s">
+        <v>43</v>
+      </c>
+      <c r="G185">
+        <v>2</v>
+      </c>
+      <c r="H185">
+        <v>1</v>
+      </c>
+      <c r="I185" t="s">
+        <v>158</v>
+      </c>
+      <c r="J185">
+        <v>2128102</v>
+      </c>
+      <c r="K185" t="b">
+        <v>0</v>
+      </c>
+      <c r="L185" t="str">
+        <f t="shared" si="3"/>
+        <v>玛格丽特雇员的升星道具</v>
+      </c>
+      <c r="O185">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15">
+      <c r="A186">
+        <v>1128201</v>
+      </c>
+      <c r="C186">
+        <v>1128201</v>
+      </c>
+      <c r="D186" t="str">
+        <f t="shared" si="2"/>
+        <v>奥古斯特碎片</v>
+      </c>
+      <c r="E186">
+        <v>2</v>
+      </c>
+      <c r="F186" t="s">
+        <v>43</v>
+      </c>
+      <c r="G186">
+        <v>3</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+      <c r="I186" t="s">
+        <v>158</v>
+      </c>
+      <c r="J186">
+        <v>2128201</v>
+      </c>
+      <c r="K186" t="b">
+        <v>0</v>
+      </c>
+      <c r="L186" t="str">
+        <f t="shared" si="3"/>
+        <v>奥古斯特雇员的升星道具</v>
+      </c>
+      <c r="O186">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15">
+      <c r="A187">
+        <v>1128202</v>
+      </c>
+      <c r="C187">
+        <v>1128202</v>
+      </c>
+      <c r="D187" t="str">
+        <f t="shared" si="2"/>
+        <v>维奥莱特碎片</v>
+      </c>
+      <c r="E187">
+        <v>2</v>
+      </c>
+      <c r="F187" t="s">
+        <v>43</v>
+      </c>
+      <c r="G187">
+        <v>3</v>
+      </c>
+      <c r="H187">
+        <v>1</v>
+      </c>
+      <c r="I187" t="s">
+        <v>158</v>
+      </c>
+      <c r="J187">
+        <v>2128202</v>
+      </c>
+      <c r="K187" t="b">
+        <v>0</v>
+      </c>
+      <c r="L187" t="str">
+        <f t="shared" si="3"/>
+        <v>维奥莱特雇员的升星道具</v>
+      </c>
+      <c r="O187">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15">
+      <c r="A188">
+        <v>1128301</v>
+      </c>
+      <c r="C188">
+        <v>1128301</v>
+      </c>
+      <c r="D188" t="str">
+        <f t="shared" si="2"/>
+        <v>费利克斯碎片</v>
+      </c>
+      <c r="E188">
+        <v>2</v>
+      </c>
+      <c r="F188" t="s">
+        <v>43</v>
+      </c>
+      <c r="G188">
+        <v>4</v>
+      </c>
+      <c r="H188">
+        <v>1</v>
+      </c>
+      <c r="I188" t="s">
+        <v>158</v>
+      </c>
+      <c r="J188">
+        <v>2128301</v>
+      </c>
+      <c r="K188" t="b">
+        <v>0</v>
+      </c>
+      <c r="L188" t="str">
+        <f t="shared" si="3"/>
+        <v>费利克斯雇员的升星道具</v>
+      </c>
+      <c r="O188">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15">
+      <c r="A189">
+        <v>1128302</v>
+      </c>
+      <c r="C189">
+        <v>1128302</v>
+      </c>
+      <c r="D189" t="str">
+        <f t="shared" si="2"/>
+        <v>维多利亚碎片</v>
+      </c>
+      <c r="E189">
+        <v>2</v>
+      </c>
+      <c r="F189" t="s">
+        <v>43</v>
+      </c>
+      <c r="G189">
+        <v>4</v>
+      </c>
+      <c r="H189">
+        <v>1</v>
+      </c>
+      <c r="I189" t="s">
+        <v>158</v>
+      </c>
+      <c r="J189">
+        <v>2128302</v>
+      </c>
+      <c r="K189" t="b">
+        <v>0</v>
+      </c>
+      <c r="L189" t="str">
+        <f t="shared" si="3"/>
+        <v>维多利亚雇员的升星道具</v>
+      </c>
+      <c r="O189">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15">
+      <c r="A190">
+        <v>1128401</v>
+      </c>
+      <c r="C190">
+        <v>1128401</v>
+      </c>
+      <c r="D190" t="str">
+        <f t="shared" si="2"/>
+        <v>阿尔弗雷德碎片</v>
+      </c>
+      <c r="E190">
+        <v>2</v>
+      </c>
+      <c r="F190" t="s">
+        <v>43</v>
+      </c>
+      <c r="G190">
+        <v>7</v>
+      </c>
+      <c r="H190">
+        <v>1</v>
+      </c>
+      <c r="I190" t="s">
+        <v>158</v>
+      </c>
+      <c r="J190">
+        <v>2128401</v>
+      </c>
+      <c r="K190" t="b">
+        <v>0</v>
+      </c>
+      <c r="L190" t="str">
+        <f t="shared" si="3"/>
+        <v>阿尔弗雷德雇员的升星道具</v>
+      </c>
+      <c r="O190">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15">
+      <c r="A191">
+        <v>1128402</v>
+      </c>
+      <c r="C191">
+        <v>1128402</v>
+      </c>
+      <c r="D191" t="str">
+        <f t="shared" si="2"/>
+        <v>伊丽莎白碎片</v>
+      </c>
+      <c r="E191">
+        <v>2</v>
+      </c>
+      <c r="F191" t="s">
+        <v>43</v>
+      </c>
+      <c r="G191">
+        <v>7</v>
+      </c>
+      <c r="H191">
+        <v>1</v>
+      </c>
+      <c r="I191" t="s">
+        <v>158</v>
+      </c>
+      <c r="J191">
+        <v>2128402</v>
+      </c>
+      <c r="K191" t="b">
+        <v>0</v>
+      </c>
+      <c r="L191" t="str">
+        <f t="shared" si="3"/>
+        <v>伊丽莎白雇员的升星道具</v>
+      </c>
+      <c r="O191">
+        <v>999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
